--- a/artfynd/A 55952-2024 artfynd.xlsx
+++ b/artfynd/A 55952-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9081,6 +9081,1266 @@
       <c r="AZ62" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129635623</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>137428336</v>
+      </c>
+      <c r="B63" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>694300</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6660006</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428336</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>137428337</v>
+      </c>
+      <c r="B64" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>694303</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6660009</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428337</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>137428338</v>
+      </c>
+      <c r="B65" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>694303</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6660011</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428338</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137428339</v>
+      </c>
+      <c r="B66" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hummelsvedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>694303</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6660014</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428339</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>137428653</v>
+      </c>
+      <c r="B67" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>694320</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6659966</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428653</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>137428654</v>
+      </c>
+      <c r="B68" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>694321</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6659987</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428654</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>137428655</v>
+      </c>
+      <c r="B69" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>694309</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6659998</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428655</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>137428656</v>
+      </c>
+      <c r="B70" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>694317</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6660032</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428656</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>137428657</v>
+      </c>
+      <c r="B71" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>694321</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6660034</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428657</t>
         </is>
       </c>
     </row>
@@ -9147,6 +10407,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
